--- a/data/file_generation/reference/data_107/D店_揽收明细_res.xlsx
+++ b/data/file_generation/reference/data_107/D店_揽收明细_res.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0206/data_107/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/output/data_107/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1CD722-1430-314D-89E6-8BD7B36577C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BB1779-A951-4A44-9169-DDCF1E9CFCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="34760" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="147">
   <si>
     <t>运单编号</t>
   </si>
@@ -62,9 +62,6 @@
     <t>客户I</t>
   </si>
   <si>
-    <t>2025-10-01 16:29:11</t>
-  </si>
-  <si>
     <t>江苏省</t>
   </si>
   <si>
@@ -83,18 +80,12 @@
     <t>NQY91378K0EB</t>
   </si>
   <si>
-    <t>2025-10-03 10:36:32</t>
-  </si>
-  <si>
     <t>湖南省</t>
   </si>
   <si>
     <t>D7VFGT8KZH8X</t>
   </si>
   <si>
-    <t>2025-10-04 12:27:01</t>
-  </si>
-  <si>
     <t>浙江省</t>
   </si>
   <si>
@@ -107,9 +98,6 @@
     <t>TWAL4BYOCEZG</t>
   </si>
   <si>
-    <t>2025-10-07 10:58:31</t>
-  </si>
-  <si>
     <t>广东省</t>
   </si>
   <si>
@@ -119,153 +107,87 @@
     <t>88KKQUI7QVT4</t>
   </si>
   <si>
-    <t>2025-10-07 10:59:40</t>
-  </si>
-  <si>
     <t>重庆</t>
   </si>
   <si>
     <t>ILGZ3R69D5I6</t>
   </si>
   <si>
-    <t>2025-10-07 11:00:23</t>
-  </si>
-  <si>
     <t>河南省</t>
   </si>
   <si>
     <t>3HAHHBUNLEF0</t>
   </si>
   <si>
-    <t>2025-10-07 11:00:25</t>
-  </si>
-  <si>
     <t>NTKRFQ3N9SAI</t>
   </si>
   <si>
-    <t>2025-10-07 11:00:28</t>
-  </si>
-  <si>
     <t>98XA1HGJD0OR</t>
   </si>
   <si>
-    <t>2025-10-07 11:01:09</t>
-  </si>
-  <si>
     <t>C1XK1FYM13RL</t>
   </si>
   <si>
-    <t>2025-10-07 11:01:11</t>
-  </si>
-  <si>
     <t>陕西省</t>
   </si>
   <si>
     <t>XSWJFCVESXQP</t>
   </si>
   <si>
-    <t>2025-10-09 16:24:59</t>
-  </si>
-  <si>
     <t>WCR9VMG2YVGY</t>
   </si>
   <si>
-    <t>2025-10-11 11:30:44</t>
-  </si>
-  <si>
     <t>R2LONX1NUGYA</t>
   </si>
   <si>
-    <t>2025-10-11 11:30:46</t>
-  </si>
-  <si>
     <t>青海省</t>
   </si>
   <si>
     <t>EF1JDZ2ZSON2</t>
   </si>
   <si>
-    <t>2025-10-13 11:22:08</t>
-  </si>
-  <si>
     <t>AP27X9YJS1SE</t>
   </si>
   <si>
-    <t>2025-10-13 11:22:10</t>
-  </si>
-  <si>
     <t>0RTFZ5MYZ8XE</t>
   </si>
   <si>
-    <t>2025-10-13 11:22:15</t>
-  </si>
-  <si>
     <t>GZLH5PKKREJJ</t>
   </si>
   <si>
-    <t>2025-10-13 11:22:16</t>
-  </si>
-  <si>
     <t>吉林省</t>
   </si>
   <si>
     <t>1P01NYFT94Z0</t>
   </si>
   <si>
-    <t>2025-10-13 11:22:20</t>
-  </si>
-  <si>
     <t>PQJON95SAMU5</t>
   </si>
   <si>
-    <t>2025-10-13 11:23:15</t>
-  </si>
-  <si>
     <t>846Z36M6N7MV</t>
   </si>
   <si>
-    <t>2025-10-13 11:24:00</t>
-  </si>
-  <si>
     <t>Q8UW07I8PJAG</t>
   </si>
   <si>
-    <t>2025-10-14 11:37:45</t>
-  </si>
-  <si>
     <t>河北省</t>
   </si>
   <si>
     <t>8PUE519IOPYK</t>
   </si>
   <si>
-    <t>2025-10-14 11:38:38</t>
-  </si>
-  <si>
     <t>2W0BNLDG25AJ</t>
   </si>
   <si>
-    <t>2025-10-14 11:38:44</t>
-  </si>
-  <si>
     <t>1N3FMDEALUMR</t>
   </si>
   <si>
-    <t>2025-10-14 11:39:11</t>
-  </si>
-  <si>
     <t>2N5H6O911XCH</t>
   </si>
   <si>
-    <t>2025-10-15 11:23:39</t>
-  </si>
-  <si>
     <t>MO588HQKMRNR</t>
   </si>
   <si>
-    <t>2025-10-15 11:23:42</t>
-  </si>
-  <si>
     <t>OXUBIYI3XOBZ</t>
   </si>
   <si>
@@ -275,78 +197,45 @@
     <t>IANVZRKCEH41</t>
   </si>
   <si>
-    <t>2025-10-15 11:23:44</t>
-  </si>
-  <si>
     <t>OHPHMP26AGW1</t>
   </si>
   <si>
-    <t>2025-10-15 11:23:45</t>
-  </si>
-  <si>
     <t>山东省</t>
   </si>
   <si>
     <t>HUJ4N5PBJJFH</t>
   </si>
   <si>
-    <t>2025-10-16 11:27:09</t>
-  </si>
-  <si>
     <t>DVA4KSRCN870</t>
   </si>
   <si>
-    <t>2025-10-16 11:30:59</t>
-  </si>
-  <si>
     <t>WZPY9ZTMQY0F</t>
   </si>
   <si>
-    <t>2025-10-17 11:56:31</t>
-  </si>
-  <si>
     <t>湖北省</t>
   </si>
   <si>
     <t>H62CPV4WPAUI</t>
   </si>
   <si>
-    <t>2025-10-17 11:57:17</t>
-  </si>
-  <si>
     <t>9GDNJKA13C8S</t>
   </si>
   <si>
-    <t>2025-10-17 11:57:43</t>
-  </si>
-  <si>
     <t>E5O01SOQFGFB</t>
   </si>
   <si>
-    <t>2025-10-18 11:47:34</t>
-  </si>
-  <si>
     <t>5P37ZNXNT0EP</t>
   </si>
   <si>
-    <t>2025-10-18 11:49:54</t>
-  </si>
-  <si>
     <t>福建省</t>
   </si>
   <si>
     <t>JK4ZNVZ1GF62</t>
   </si>
   <si>
-    <t>2025-10-18 11:50:04</t>
-  </si>
-  <si>
     <t>GTQI101507MP</t>
   </si>
   <si>
-    <t>2025-10-20 09:23:15</t>
-  </si>
-  <si>
     <t>UIH782EL1I6N</t>
   </si>
   <si>
@@ -371,213 +260,120 @@
     <t>5AHMLAMYPWOR</t>
   </si>
   <si>
-    <t>2025-10-21 11:59:28</t>
-  </si>
-  <si>
     <t>甘肃省</t>
   </si>
   <si>
     <t>WM6G03NW1WDN</t>
   </si>
   <si>
-    <t>2025-10-21 12:01:14</t>
-  </si>
-  <si>
     <t>贵州省</t>
   </si>
   <si>
     <t>15BQ0WGR0LKM</t>
   </si>
   <si>
-    <t>2025-10-21 12:01:16</t>
-  </si>
-  <si>
     <t>14EZNE4N4G1G</t>
   </si>
   <si>
-    <t>2025-10-21 12:01:18</t>
-  </si>
-  <si>
     <t>LDZALLX5GZWT</t>
   </si>
   <si>
-    <t>2025-10-21 12:01:21</t>
-  </si>
-  <si>
     <t>SZL9AWZ60O2U</t>
   </si>
   <si>
-    <t>2025-10-21 12:01:26</t>
-  </si>
-  <si>
     <t>AT1I7BOCCVUR</t>
   </si>
   <si>
-    <t>2025-10-21 12:01:27</t>
-  </si>
-  <si>
     <t>广西壮族自治区</t>
   </si>
   <si>
     <t>XC84G351ZAA4</t>
   </si>
   <si>
-    <t>2025-10-22 11:15:32</t>
-  </si>
-  <si>
     <t>L6HLF2ZY38FB</t>
   </si>
   <si>
-    <t>2025-10-22 11:15:36</t>
-  </si>
-  <si>
     <t>2NQVSD0QKAVT</t>
   </si>
   <si>
-    <t>2025-10-22 11:15:39</t>
-  </si>
-  <si>
     <t>天津</t>
   </si>
   <si>
     <t>EJQ9ZHL2W343</t>
   </si>
   <si>
-    <t>2025-10-22 11:15:42</t>
-  </si>
-  <si>
     <t>WPGAR8SHDV80</t>
   </si>
   <si>
     <t>Y2PQLXNLT28N</t>
   </si>
   <si>
-    <t>2025-10-22 11:15:58</t>
-  </si>
-  <si>
     <t>KL4CW9D420VP</t>
   </si>
   <si>
-    <t>2025-10-22 11:16:01</t>
-  </si>
-  <si>
     <t>5OCV412H1HAB</t>
   </si>
   <si>
-    <t>2025-10-22 11:16:16</t>
-  </si>
-  <si>
     <t>D93V0E0VJND2</t>
   </si>
   <si>
-    <t>2025-10-22 11:16:51</t>
-  </si>
-  <si>
     <t>6UCOVJ86NURM</t>
   </si>
   <si>
-    <t>2025-10-22 11:18:09</t>
-  </si>
-  <si>
     <t>T19D0DKD3NJY</t>
   </si>
   <si>
-    <t>2025-10-22 11:18:10</t>
-  </si>
-  <si>
     <t>SWAPQOH2LO3J</t>
   </si>
   <si>
-    <t>2025-10-22 11:18:12</t>
-  </si>
-  <si>
     <t>I8YR2U94C4T3</t>
   </si>
   <si>
-    <t>2025-10-22 11:18:15</t>
-  </si>
-  <si>
     <t>FXQBWN110T84</t>
   </si>
   <si>
-    <t>2025-10-22 11:19:20</t>
-  </si>
-  <si>
     <t>OI21VNHOTPNL</t>
   </si>
   <si>
-    <t>2025-10-22 11:19:22</t>
-  </si>
-  <si>
     <t>CDIM2VRJS6E7</t>
   </si>
   <si>
-    <t>2025-10-23 11:23:59</t>
-  </si>
-  <si>
     <t>宁夏回族自治区</t>
   </si>
   <si>
     <t>K7F30MZ2GZCW</t>
   </si>
   <si>
-    <t>2025-10-23 11:24:05</t>
-  </si>
-  <si>
     <t>APH4HNZU5MPY</t>
   </si>
   <si>
-    <t>2025-10-23 11:24:07</t>
-  </si>
-  <si>
     <t>84SP8AWY1HMY</t>
   </si>
   <si>
-    <t>2025-10-23 11:24:11</t>
-  </si>
-  <si>
     <t>OK5X0ZSEIUIQ</t>
   </si>
   <si>
-    <t>2025-10-25 12:52:29</t>
-  </si>
-  <si>
     <t>292P9IYK0F34</t>
   </si>
   <si>
-    <t>2025-10-27 15:50:04</t>
-  </si>
-  <si>
     <t>1C31HNF7V33L</t>
   </si>
   <si>
     <t>CQQ50P0SMSC5</t>
   </si>
   <si>
-    <t>2025-10-27 15:50:05</t>
-  </si>
-  <si>
     <t>5NAF2HQQBPKQ</t>
   </si>
   <si>
-    <t>2025-10-29 14:47:27</t>
-  </si>
-  <si>
     <t>OL6IOMGYYG7W</t>
   </si>
   <si>
-    <t>2025-10-07 11:00:27</t>
-  </si>
-  <si>
     <t>北京</t>
   </si>
   <si>
     <t>XYUUZ0JTF0SH</t>
   </si>
   <si>
-    <t>2025-10-16 11:27:11</t>
-  </si>
-  <si>
     <t>PKCGCHXQOYD9</t>
   </si>
   <si>
@@ -587,147 +383,81 @@
     <t>X88OHRUOH9W7</t>
   </si>
   <si>
-    <t>2025-10-29 14:46:54</t>
-  </si>
-  <si>
     <t>上海</t>
   </si>
   <si>
     <t>0W83T6JUY9LX</t>
   </si>
   <si>
-    <t>2025-10-06 18:16:45</t>
-  </si>
-  <si>
     <t>WTL1Q18HIIQV</t>
   </si>
   <si>
-    <t>2025-10-13 11:24:05</t>
-  </si>
-  <si>
     <t>GQD7HBBVLO8Y</t>
   </si>
   <si>
-    <t>2025-10-03 10:37:05</t>
-  </si>
-  <si>
     <t>OCSIZ6KA1UC6</t>
   </si>
   <si>
-    <t>2025-10-17 11:57:15</t>
-  </si>
-  <si>
     <t>RQIL8FGEDRCP</t>
   </si>
   <si>
     <t>LIPDPFUX8Q0A</t>
   </si>
   <si>
-    <t>2025-10-09 16:25:21</t>
-  </si>
-  <si>
     <t>9UZJK95O2R55</t>
   </si>
   <si>
-    <t>2025-10-22 11:19:03</t>
-  </si>
-  <si>
     <t>SQXGLLHQUYIG</t>
   </si>
   <si>
-    <t>2025-10-09 16:25:22</t>
-  </si>
-  <si>
     <t>725H66SHUDT7</t>
   </si>
   <si>
-    <t>2025-10-06 12:06:38</t>
-  </si>
-  <si>
     <t>BTFFYTFWTQD0</t>
   </si>
   <si>
-    <t>2025-10-14 11:37:59</t>
-  </si>
-  <si>
     <t>LEV5HK19BKAU</t>
   </si>
   <si>
-    <t>2025-10-06 18:16:15</t>
-  </si>
-  <si>
     <t>50P9JFH86ACF</t>
   </si>
   <si>
-    <t>2025-10-05 11:54:52</t>
-  </si>
-  <si>
     <t>NR373G9IANKO</t>
   </si>
   <si>
     <t>31BU3AWD61HL</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:18</t>
-  </si>
-  <si>
     <t>YOST83I0TSL5</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:32</t>
-  </si>
-  <si>
     <t>NVFZOBXQIV2L</t>
   </si>
   <si>
-    <t>2025-10-14 11:37:58</t>
-  </si>
-  <si>
     <t>VRR354XPPYLK</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:14</t>
-  </si>
-  <si>
     <t>7JFN5573PM48</t>
   </si>
   <si>
-    <t>2025-10-06 18:16:18</t>
-  </si>
-  <si>
     <t>QT338VIQRU74</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:09</t>
-  </si>
-  <si>
     <t>PMXR783H54N8</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:25</t>
-  </si>
-  <si>
     <t>LMCPVR7S0ODQ</t>
   </si>
   <si>
     <t>1QABZ7E1J1XX</t>
   </si>
   <si>
-    <t>2025-10-05 11:54:57</t>
-  </si>
-  <si>
     <t>0ZFLFK95JGNL</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:30</t>
-  </si>
-  <si>
     <t>FFTZU8T3RE0K</t>
   </si>
   <si>
-    <t>2025-10-04 17:52:53</t>
-  </si>
-  <si>
     <t>2S0SMHDNHFT9</t>
   </si>
   <si>
@@ -737,19 +467,13 @@
     <t>0D70IUL0VZQN</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:08</t>
-  </si>
-  <si>
     <t>6S54NL49FV2H</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:13</t>
-  </si>
-  <si>
     <t>KKKBY4Z67IFT</t>
   </si>
   <si>
-    <t>2025-10-05 11:55:20</t>
+    <t>2025年10月</t>
   </si>
 </sst>
 </file>
@@ -1150,22 +874,22 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2">
+        <v>0.2</v>
+      </c>
+      <c r="F2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
-        <v>0.2</v>
-      </c>
-      <c r="F2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="I2">
         <f>ROUND(301.5-110*1.8,2)</f>
@@ -1174,16 +898,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
       </c>
       <c r="E3">
         <v>0.57999999999999996</v>
@@ -1194,16 +918,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -1214,16 +938,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>0.2</v>
@@ -1234,16 +958,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
         <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
       </c>
       <c r="E6">
         <v>0.2</v>
@@ -1254,16 +978,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>0.2</v>
@@ -1274,16 +998,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>0.2</v>
@@ -1294,16 +1018,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>0.28999999999999998</v>
@@ -1314,16 +1038,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E10">
         <v>0.2</v>
@@ -1334,16 +1058,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E11">
         <v>0.2</v>
@@ -1354,16 +1078,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -1374,16 +1098,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E13">
         <v>0.2</v>
@@ -1394,16 +1118,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E14">
         <v>0.2</v>
@@ -1414,16 +1138,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>0.2</v>
@@ -1434,16 +1158,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16">
         <v>0.2</v>
@@ -1454,16 +1178,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>0.2</v>
@@ -1474,16 +1198,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -1494,16 +1218,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>0.2</v>
@@ -1514,16 +1238,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>0.2</v>
@@ -1534,16 +1258,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>0.2</v>
@@ -1554,16 +1278,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E22">
         <v>0.2</v>
@@ -1574,16 +1298,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>0.57999999999999996</v>
@@ -1594,16 +1318,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <v>0.67</v>
@@ -1614,16 +1338,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E25">
         <v>0.44</v>
@@ -1634,16 +1358,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E26">
         <v>0.2</v>
@@ -1654,16 +1378,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27">
         <v>0.5</v>
@@ -1674,16 +1398,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E28">
         <v>0.51</v>
@@ -1694,16 +1418,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29">
         <v>0.54</v>
@@ -1714,16 +1438,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E30">
         <v>0.2</v>
@@ -1734,16 +1458,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E31">
         <v>0.2</v>
@@ -1754,16 +1478,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E32">
         <v>0.2</v>
@@ -1774,16 +1498,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E33">
         <v>0.2</v>
@@ -1794,16 +1518,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E34">
         <v>0.2</v>
@@ -1814,16 +1538,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35">
         <v>0.4</v>
@@ -1834,16 +1558,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E36">
         <v>0.2</v>
@@ -1854,16 +1578,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E37">
         <v>0.2</v>
@@ -1874,16 +1598,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E38">
         <v>0.43</v>
@@ -1894,16 +1618,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E39">
         <v>0.76</v>
@@ -1914,16 +1638,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>0.2</v>
@@ -1934,16 +1658,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E41">
         <v>0.2</v>
@@ -1954,16 +1678,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E42">
         <v>0.2</v>
@@ -1974,16 +1698,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E43">
         <v>0.2</v>
@@ -1994,16 +1718,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E44">
         <v>0.2</v>
@@ -2014,16 +1738,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E45">
         <v>0.2</v>
@@ -2034,16 +1758,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46">
         <v>0.2</v>
@@ -2054,16 +1778,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E47">
         <v>0.2</v>
@@ -2074,16 +1798,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="E48">
         <v>0.2</v>
@@ -2094,16 +1818,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="E49">
         <v>0.2</v>
@@ -2114,16 +1838,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E50">
         <v>0.2</v>
@@ -2134,16 +1858,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E51">
         <v>0.25</v>
@@ -2154,16 +1878,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>0.42</v>
@@ -2174,16 +1898,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E53">
         <v>0.35</v>
@@ -2194,16 +1918,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="E54">
         <v>0.35</v>
@@ -2214,16 +1938,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E55">
         <v>0.76</v>
@@ -2234,16 +1958,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s">
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E56">
         <v>0.2</v>
@@ -2254,16 +1978,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="E57">
         <v>0.2</v>
@@ -2274,16 +1998,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E58">
         <v>0.2</v>
@@ -2294,16 +2018,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E59">
         <v>0.2</v>
@@ -2314,16 +2038,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E60">
         <v>0.9</v>
@@ -2334,16 +2058,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="B61" t="s">
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E61">
         <v>0.49</v>
@@ -2354,16 +2078,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E62">
         <v>0.52</v>
@@ -2374,16 +2098,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="B63" t="s">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="E63">
         <v>0.51</v>
@@ -2394,16 +2118,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E64">
         <v>0.96</v>
@@ -2414,16 +2138,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E65">
         <v>0.52</v>
@@ -2434,16 +2158,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E66">
         <v>0.2</v>
@@ -2454,16 +2178,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="B67" t="s">
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E67">
         <v>0.5</v>
@@ -2474,16 +2198,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E68">
         <v>0.54</v>
@@ -2494,16 +2218,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E69">
         <v>0.45</v>
@@ -2514,16 +2238,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D70" t="s">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="E70">
         <v>0.69</v>
@@ -2534,16 +2258,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="E71">
         <v>0.2</v>
@@ -2554,16 +2278,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E72">
         <v>0.2</v>
@@ -2574,16 +2298,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E73">
         <v>0.41</v>
@@ -2594,16 +2318,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="B74" t="s">
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E74">
         <v>0.23</v>
@@ -2614,16 +2338,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="B75" t="s">
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E75">
         <v>0.2</v>
@@ -2634,16 +2358,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>0.2</v>
@@ -2654,16 +2378,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="D77" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E77">
         <v>0.2</v>
@@ -2674,16 +2398,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="E78">
         <v>0.2</v>
@@ -2694,16 +2418,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="B79" t="s">
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="D79" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="E79">
         <v>0.2</v>
@@ -2714,16 +2438,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="D80" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="E80">
         <v>0.2</v>
@@ -2734,16 +2458,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="B81" t="s">
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D81" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="E81">
         <v>0.2</v>
@@ -2754,16 +2478,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="B82" t="s">
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="E82">
         <v>0.2</v>
@@ -2774,16 +2498,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="D83" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="E83">
         <v>0.71</v>
@@ -2794,16 +2518,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>188</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="D84" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E84">
         <v>1.02</v>
@@ -2814,16 +2538,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="B85" t="s">
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E85">
         <v>1.03</v>
@@ -2834,16 +2558,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>192</v>
+        <v>120</v>
       </c>
       <c r="B86" t="s">
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E86">
         <v>1.03</v>
@@ -2854,16 +2578,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="B87" t="s">
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E87">
         <v>1.18</v>
@@ -2874,16 +2598,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="B88" t="s">
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E88">
         <v>1.4</v>
@@ -2894,16 +2618,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="B89" t="s">
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="D89" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E89">
         <v>1.4</v>
@@ -2914,16 +2638,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="B90" t="s">
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E90">
         <v>1.54</v>
@@ -2934,16 +2658,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>201</v>
+        <v>125</v>
       </c>
       <c r="B91" t="s">
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="D91" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E91">
         <v>1.61</v>
@@ -2954,16 +2678,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="B92" t="s">
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92">
         <v>1.63</v>
@@ -2974,16 +2698,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>127</v>
       </c>
       <c r="B93" t="s">
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="D93" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="E93">
         <v>1.91</v>
@@ -2994,16 +2718,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="B94" t="s">
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="D94" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E94">
         <v>2.59</v>
@@ -3014,16 +2738,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>129</v>
       </c>
       <c r="B95" t="s">
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E95">
         <v>2.72</v>
@@ -3034,16 +2758,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="B96" t="s">
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="D96" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E96">
         <v>2.73</v>
@@ -3054,16 +2778,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="B97" t="s">
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>146</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E97">
         <v>2.74</v>
@@ -3074,16 +2798,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E98">
         <v>2.76</v>
@@ -3094,16 +2818,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="D99" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E99">
         <v>2.77</v>
@@ -3114,16 +2838,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="B100" t="s">
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="E100">
         <v>2.78</v>
@@ -3134,16 +2858,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>221</v>
+        <v>146</v>
       </c>
       <c r="D101" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E101">
         <v>2.79</v>
@@ -3154,16 +2878,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="B102" t="s">
         <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="D102" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E102">
         <v>2.8</v>
@@ -3174,16 +2898,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="B103" t="s">
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="D103" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E103">
         <v>2.81</v>
@@ -3194,16 +2918,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="B104" t="s">
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="D104" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="E104">
         <v>2.83</v>
@@ -3214,16 +2938,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>227</v>
+        <v>139</v>
       </c>
       <c r="B105" t="s">
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E105">
         <v>2.88</v>
@@ -3234,16 +2958,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>229</v>
+        <v>140</v>
       </c>
       <c r="B106" t="s">
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>230</v>
+        <v>146</v>
       </c>
       <c r="D106" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="E106">
         <v>2.88</v>
@@ -3254,16 +2978,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="B107" t="s">
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="D107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E107">
         <v>2.89</v>
@@ -3274,16 +2998,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="B108" t="s">
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="D108" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E108">
         <v>2.91</v>
@@ -3294,16 +3018,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="B109" t="s">
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>234</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="E109">
         <v>2.98</v>
@@ -3314,16 +3038,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="B110" t="s">
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E110">
         <v>2.98</v>
@@ -3334,16 +3058,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>237</v>
+        <v>145</v>
       </c>
       <c r="B111" t="s">
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E111">
         <v>2.99</v>
@@ -3522,13 +3246,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC8C5A96-04FA-41DE-96F5-343AB1B0C922}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010B6622-3A12-4114-8F5B-3FC3B6F665C6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E86611-F9DA-42DE-8F6B-3DB1B970DB7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{609ED1A1-C3A6-4927-B9D7-227AE524DF29}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4DE57A5-DB67-4F94-BA66-080CF52673C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D642EB-7FDB-43A6-A45C-55A20C069BBE}"/>
 </file>